--- a/VerveStacks_FRA_grids_kan25/SubRES_Tmpl/SubRES_Data_Centers.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SubRES_Tmpl/SubRES_Data_Centers.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_FRA_grids_kan25\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{669D10A2-D74B-4793-AB9E-50EF39060A37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7740094D-AB43-49AF-9ED1-6F3D944BF79C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="data centers" sheetId="9" r:id="rId1"/>
+    <sheet name="README" sheetId="10" r:id="rId1"/>
+    <sheet name="data centers" sheetId="9" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
     <definedName name="FuelList">[1]ELC_Lists!$K$4:$K$113</definedName>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="58">
   <si>
     <t>~FI_Comm</t>
   </si>
@@ -170,6 +171,62 @@
   </si>
   <si>
     <t>ncap_bnd~fx~0</t>
+  </si>
+  <si>
+    <t>Data Centers SubRES - approach</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Explore the new generation capacity and grid expansion implied by data center demand growth. Data centers are modeled as exogenous, cost-free electric loads pinned to specific grid substations; the model's only freedom is how to serve them.</t>
+  </si>
+  <si>
+    <t>Design</t>
+  </si>
+  <si>
+    <t>1. Processes</t>
+  </si>
+  <si>
+    <t>Five DMD processes DC_1..DC_5 (GW / TWh), each sited at a 400 kV substation node: DC_1 Paris, DC_2 Dunkirk, DC_3 Toulouse, DC_4 Lyon, DC_5 Nice. Input topology to the e_w*-400_FRA node commodities is set via ~TFM_TOPINS in the Trans file. EFF=1, CAP2ACT=8.76 (GW -&gt; TWh/yr).</t>
+  </si>
+  <si>
+    <t>2. Capacity</t>
+  </si>
+  <si>
+    <t>The build profile is hardwired with NCAP_PASTI (Trans file, ~TFM_INS-TS): staggered additions 2026-2032 totalling 8 GW (DC_1: 2, DC_2: 2, DC_3: 2, DC_4: 1, DC_5: 1). Endogenous investment is blocked by NCAP_BND~FX~0 = 2 in ~FI_T: year 0 is the I/E control record, option code 2 fills all years outside the (empty) data window with zero, so NCAP_BND FX = 0 everywhere.</t>
+  </si>
+  <si>
+    <t>3. Operation</t>
+  </si>
+  <si>
+    <t>NCAP_AF~FX = 0.85 from 2025 (I/E option 3: interpolate + extrapolate forward) forces every DC to run at exactly 85% of installed capacity. No dispatch freedom - capacity plus AF fully determine the annual load.</t>
+  </si>
+  <si>
+    <t>4. Load profile</t>
+  </si>
+  <si>
+    <t>Each DC outputs to two DEM commodities, DCdem_industry and DCdem_buildings. These carry no COM_PROJ - they exist purely as profile carriers. The TSParameters scenarios (e.g. Scen_TSParameters_ts_12, sheet load_demand_peak_hydro) assign COM_FR to *[_]industry and *[_]buildings by wildcard, so the DC commodities inherit the sectoral load shapes by naming convention. The forced output is distributed across timeslices by COM_FR, and with EFF=1 the electricity drawn at each grid node carries the same shape.</t>
+  </si>
+  <si>
+    <t>5. Shape mix</t>
+  </si>
+  <si>
+    <t>The split between the (flat) industry shape and the (peakier) buildings shape is the lever for how flat vs. peaky the DC load appears to the grid. A FLO_SHAR constraint on the two outputs is planned but not yet in place; until then the split is free.</t>
+  </si>
+  <si>
+    <t>Open items</t>
+  </si>
+  <si>
+    <t>- FLO_SHAR between DCdem_industry and DCdem_buildings outputs.
+- Verify peak-equation treatment: com_pkflx applies to ELC; check how the e_w*-400_FRA node commodities enter the peaking constraint.</t>
+  </si>
+  <si>
+    <t>Files</t>
+  </si>
+  <si>
+    <t>SubRES_Data_Centers.xlsx: ~FI_Comm (DEM commodities), ~fi_process (DC_1..DC_5), ~fi_t (LIFE, NCAP_BND I/E block, COMM-OUT).
+SubRES_Data_Centers_Trans.xlsx: siting key, ~TFM_TOPINS (grid node inputs), ~TFM_INS (CAP2ACT, EFF), ~TFM_INS-TS (NCAP_PASTI builds, NCAP_AF FX 0.85).</t>
   </si>
 </sst>
 </file>
@@ -180,7 +237,7 @@
     <numFmt numFmtId="164" formatCode="\Te\x\t"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,6 +295,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -282,9 +355,24 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="14">
     <cellStyle name="20% - Accent3 3 2" xfId="3" xr:uid="{ABC4988B-8BA7-47D0-A9D6-448C999748B6}"/>
@@ -677,6 +765,132 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F16FD0-875D-4F24-BE75-ACA06D8C9550}">
+  <dimension ref="B2:C20"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="18.59765625" customWidth="1"/>
+    <col min="3" max="3" width="110.59765625" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" ht="18">
+      <c r="B2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="4"/>
+    </row>
+    <row r="3" spans="2:3">
+      <c r="B3" s="5"/>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" spans="2:3" ht="28.5">
+      <c r="B4" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="B5" s="5"/>
+      <c r="C5" s="4"/>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="B6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="4"/>
+    </row>
+    <row r="7" spans="2:3" ht="42.75">
+      <c r="B7" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="42.75">
+      <c r="B8" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="28.5">
+      <c r="B9" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="57">
+      <c r="B10" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" ht="28.5">
+      <c r="B11" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3">
+      <c r="B12" s="5"/>
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" spans="2:3" ht="42.75">
+      <c r="B13" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3">
+      <c r="B14" s="5"/>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="2:3" ht="42.75">
+      <c r="B15" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3">
+      <c r="B16" s="5"/>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" s="5"/>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" s="5"/>
+      <c r="C18" s="4"/>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19" s="5"/>
+      <c r="C19" s="4"/>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" s="5"/>
+      <c r="C20" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FD6D8AA-F8A9-4BBE-94C7-C767CA3BCC03}">
   <dimension ref="B2:I25"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
